--- a/docs/特殊發音.xlsx
+++ b/docs/特殊發音.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>學富五車</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -45,6 +45,14 @@
   </si>
   <si>
     <t>文字</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>菲薄</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>斐博</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -305,7 +313,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -344,6 +352,14 @@
         <v>5</v>
       </c>
     </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/特殊發音.xlsx
+++ b/docs/特殊發音.xlsx
@@ -48,11 +48,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>菲薄</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>斐博</t>
+    <t>妄自菲薄</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>妄自斐博</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
